--- a/files/档案材料/0710/工商部中华国货展览会实录Y009-001-00366/参展人数统计.xlsx
+++ b/files/档案材料/0710/工商部中华国货展览会实录Y009-001-00366/参展人数统计.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AAA好好读书\aaa史料收集\shiliao_website\files\档案材料\0710\工商部中华国货展览会实录Y009-001-00366\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB3C7FB-3219-4AE4-BCCD-912F5E1C74EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BCC5C1-5401-4C1B-B906-1F70E3F78BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{957EF486-F74E-4D1F-8DD1-D584CF4E192C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{957EF486-F74E-4D1F-8DD1-D584CF4E192C}"/>
   </bookViews>
   <sheets>
     <sheet name="十二月统计" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
   <si>
     <t>日期</t>
   </si>
@@ -331,12 +331,90 @@
     <t>本日合计</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>合计</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>团体总人数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>12月参展人数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1月参展人数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>参观时段</t>
+  </si>
+  <si>
+    <t>特别来宾（人）</t>
+  </si>
+  <si>
+    <t>团体参观者（人）</t>
+  </si>
+  <si>
+    <t>普通来宾（人）</t>
+  </si>
+  <si>
+    <t>参观总人数（人）</t>
+  </si>
+  <si>
+    <t>12 月展期</t>
+  </si>
+  <si>
+    <t>次年 1 月展期</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>次年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,6 +479,23 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -422,7 +517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -445,13 +540,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -487,6 +634,27 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -802,13 +970,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{539B33D6-605A-4EEE-8E9C-8D9503761A97}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>38</v>
       </c>
@@ -832,7 +1000,7 @@
       </c>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -855,7 +1023,7 @@
         <v>9309</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -878,7 +1046,7 @@
         <v>19309</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -901,7 +1069,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
@@ -923,8 +1091,11 @@
       <c r="G5" s="7">
         <v>4402</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="P5" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -946,8 +1117,23 @@
       <c r="G6" s="7">
         <v>5904</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="N6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
@@ -969,8 +1155,24 @@
       <c r="G7" s="7">
         <v>5105</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="N7" s="10">
+        <v>485</v>
+      </c>
+      <c r="O7" s="10">
+        <v>136</v>
+      </c>
+      <c r="P7" s="10">
+        <v>10710</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>202100</v>
+      </c>
+      <c r="R7" s="10">
+        <f>N7+P7+Q7</f>
+        <v>213295</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
@@ -992,8 +1194,11 @@
       <c r="G8" s="7">
         <v>5593</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="P8" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -1015,8 +1220,23 @@
       <c r="G9" s="7">
         <v>2271</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="N9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -1038,8 +1258,24 @@
       <c r="G10" s="7">
         <v>7055</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="N10" s="10">
+        <v>209</v>
+      </c>
+      <c r="O10" s="10">
+        <v>0</v>
+      </c>
+      <c r="P10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>117000</v>
+      </c>
+      <c r="R10" s="10">
+        <f>209+P10+Q10</f>
+        <v>117209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1062,7 +1298,7 @@
         <v>6307</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
@@ -1085,7 +1321,7 @@
         <v>5462</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>19</v>
       </c>
@@ -1108,7 +1344,7 @@
         <v>2956</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>52</v>
       </c>
@@ -1130,8 +1366,23 @@
       <c r="G14" s="7">
         <v>3101</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="N14" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="P14" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q14" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="R14" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>20</v>
       </c>
@@ -1153,8 +1404,23 @@
       <c r="G15" s="7">
         <v>2306</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="N15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" s="12">
+        <v>485</v>
+      </c>
+      <c r="P15" s="12">
+        <v>10710</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>202100</v>
+      </c>
+      <c r="R15" s="12">
+        <v>213295</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>21</v>
       </c>
@@ -1176,8 +1442,23 @@
       <c r="G16" s="7">
         <v>3927</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="N16" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="O16" s="12">
+        <v>209</v>
+      </c>
+      <c r="P16" s="12">
+        <v>21280</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>117000</v>
+      </c>
+      <c r="R16" s="12">
+        <v>138489</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>22</v>
       </c>
@@ -1200,7 +1481,7 @@
         <v>12316</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="43.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>23</v>
       </c>
@@ -1222,8 +1503,23 @@
       <c r="G18" s="7">
         <v>6607</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="N18" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="P18" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>24</v>
       </c>
@@ -1245,8 +1541,23 @@
       <c r="G19" s="7">
         <v>6403</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="N19" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="O19" s="17">
+        <v>485</v>
+      </c>
+      <c r="P19" s="17">
+        <v>10710</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>202100</v>
+      </c>
+      <c r="R19" s="17">
+        <v>213295</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
@@ -1268,8 +1579,23 @@
       <c r="G20" s="7">
         <v>5857</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="N20" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="O20" s="17">
+        <v>209</v>
+      </c>
+      <c r="P20" s="17">
+        <v>21280</v>
+      </c>
+      <c r="Q20" s="17">
+        <v>117000</v>
+      </c>
+      <c r="R20" s="17">
+        <v>138489</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>26</v>
       </c>
@@ -1292,7 +1618,7 @@
         <v>6005</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>27</v>
       </c>
@@ -1315,7 +1641,7 @@
         <v>6617</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>28</v>
       </c>
@@ -1338,7 +1664,7 @@
         <v>12608</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>29</v>
       </c>
@@ -1361,7 +1687,7 @@
         <v>12584</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>30</v>
       </c>
@@ -1384,7 +1710,7 @@
         <v>4554</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>31</v>
       </c>
@@ -1407,7 +1733,7 @@
         <v>13849</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>32</v>
       </c>
@@ -1430,7 +1756,7 @@
         <v>7403</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>33</v>
       </c>
@@ -1453,7 +1779,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>34</v>
       </c>
@@ -1476,7 +1802,7 @@
         <v>4311</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>35</v>
       </c>
@@ -1499,7 +1825,7 @@
         <v>6808</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>36</v>
       </c>
@@ -1522,7 +1848,7 @@
         <v>9426</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
